--- a/2 Test Cases/Test Cases.xlsx
+++ b/2 Test Cases/Test Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\Project 1- On manual testing\2 Test Cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\Manual-Testing---OrangeHRM-Demo-Website-\2 Test Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6347315-E372-44BB-9FE0-5A1B292C7876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8382D2E8-D49D-43DB-A37D-C7E4AE8ECB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,9 +756,6 @@
     <t>Verify user can leave empty input in the middle name field</t>
   </si>
   <si>
-    <t>Google Chrome</t>
-  </si>
-  <si>
     <t>My Info
 Personal Details</t>
   </si>
@@ -1607,6 +1604,10 @@
   </si>
   <si>
     <t>TC_69</t>
+  </si>
+  <si>
+    <t>Windows 11, 
+Google Chrome</t>
   </si>
 </sst>
 </file>
@@ -1748,49 +1749,7 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill>
@@ -1915,34 +1874,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}" name="Table2" displayName="Table2" ref="A1:B7" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}" name="Table2" displayName="Table2" ref="A1:B7" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="A1:B7" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CCDBE3D5-BA30-452E-909C-7F873D8A70DA}" name="Name" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{A5779E73-DBC0-465F-900A-DD37322B0CB2}" name="Information" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{CCDBE3D5-BA30-452E-909C-7F873D8A70DA}" name="Name" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{A5779E73-DBC0-465F-900A-DD37322B0CB2}" name="Information" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}" name="Table3" displayName="Table3" ref="A9:N78" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}" name="Table3" displayName="Table3" ref="A9:N78" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A9:N78" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}"/>
   <tableColumns count="14">
-    <tableColumn id="3" xr3:uid="{79DE2349-3CBC-4143-8CC4-2A916E332E1A}" name="Test Case ID" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{072E7757-2DD7-4D82-9E34-BD6B56024F46}" name="Test Case Title" dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{84819441-F443-4D12-9CA1-9068D48C8291}" name="Module" dataDxfId="23" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{EA95E4DF-21F9-4B1B-B053-F3C10576A572}" name="Preconditions" dataDxfId="22" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{C41CB108-4FDE-48FA-A32A-530EC33A9B95}" name="Steps" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{76C9D7D3-DEF7-446D-98B7-1E0A8B648542}" name="Test Data" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{AB0270D7-8FB5-43C0-BFC2-362BB1C6DB6A}" name="Priority" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{ABB40573-C686-422F-AF00-46C25CEC899A}" name="Severity" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{CCCFA774-F91F-4816-BA60-27DE55A487FF}" name="Expected Result" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{71D61FE6-98A2-4210-837C-F2BBF530F9E5}" name="Actual Result" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{AB495624-3700-40F0-9D3F-4A48458D2841}" name="Testing environment" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{1C2CA1F8-A497-48AD-8741-469AE5F239CA}" name="Status" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{0BA41AF9-03FC-4396-BE33-D5B87DA0A07D}" name="Attachment " dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{42278E2B-9A99-4E11-A447-FD44432F578F}" name="Comments / Notes" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{79DE2349-3CBC-4143-8CC4-2A916E332E1A}" name="Test Case ID" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{072E7757-2DD7-4D82-9E34-BD6B56024F46}" name="Test Case Title" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{84819441-F443-4D12-9CA1-9068D48C8291}" name="Module" dataDxfId="17" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{EA95E4DF-21F9-4B1B-B053-F3C10576A572}" name="Preconditions" dataDxfId="16" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{C41CB108-4FDE-48FA-A32A-530EC33A9B95}" name="Steps" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{76C9D7D3-DEF7-446D-98B7-1E0A8B648542}" name="Test Data" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{AB0270D7-8FB5-43C0-BFC2-362BB1C6DB6A}" name="Priority" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{ABB40573-C686-422F-AF00-46C25CEC899A}" name="Severity" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{CCCFA774-F91F-4816-BA60-27DE55A487FF}" name="Expected Result" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{71D61FE6-98A2-4210-837C-F2BBF530F9E5}" name="Actual Result" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{AB495624-3700-40F0-9D3F-4A48458D2841}" name="Testing environment" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{1C2CA1F8-A497-48AD-8741-469AE5F239CA}" name="Status" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{0BA41AF9-03FC-4396-BE33-D5B87DA0A07D}" name="Attachment " dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{42278E2B-9A99-4E11-A447-FD44432F578F}" name="Comments / Notes" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2245,7 +2204,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -2361,16 +2320,16 @@
         <v>138</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N10" s="6"/>
     </row>
@@ -2398,19 +2357,19 @@
         <v>28</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N11" s="6"/>
     </row>
@@ -2438,19 +2397,19 @@
         <v>28</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N12" s="6"/>
     </row>
@@ -2478,19 +2437,19 @@
         <v>28</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N13" s="6"/>
     </row>
@@ -2518,19 +2477,19 @@
         <v>27</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N14" s="6"/>
     </row>
@@ -2558,19 +2517,19 @@
         <v>27</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N15" s="6"/>
     </row>
@@ -2582,7 +2541,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>25</v>
@@ -2600,19 +2559,19 @@
         <v>28</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -2641,19 +2600,19 @@
         <v>28</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
@@ -2682,19 +2641,19 @@
         <v>28</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -2723,19 +2682,19 @@
         <v>28</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -2764,19 +2723,19 @@
         <v>28</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -2805,19 +2764,19 @@
         <v>28</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
@@ -2846,19 +2805,19 @@
         <v>28</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
@@ -2887,19 +2846,19 @@
         <v>28</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L23" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
@@ -2928,19 +2887,19 @@
         <v>28</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L24" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2969,19 +2928,19 @@
         <v>28</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
@@ -3010,19 +2969,19 @@
         <v>28</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -3051,19 +3010,19 @@
         <v>28</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>55</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -3092,19 +3051,19 @@
         <v>28</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
@@ -3133,19 +3092,19 @@
         <v>28</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
@@ -3174,19 +3133,19 @@
         <v>28</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
@@ -3215,19 +3174,19 @@
         <v>28</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
@@ -3256,19 +3215,19 @@
         <v>28</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
@@ -3297,19 +3256,19 @@
         <v>28</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3338,19 +3297,19 @@
         <v>28</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3379,19 +3338,19 @@
         <v>28</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -3420,19 +3379,19 @@
         <v>28</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
@@ -3461,19 +3420,19 @@
         <v>28</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
@@ -3502,19 +3461,19 @@
         <v>28</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
@@ -3543,19 +3502,19 @@
         <v>28</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M39" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
@@ -3584,19 +3543,19 @@
         <v>28</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -3625,19 +3584,19 @@
         <v>28</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M41" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
@@ -3666,19 +3625,19 @@
         <v>28</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -3707,19 +3666,19 @@
         <v>28</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M43" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N43" s="6"/>
     </row>
@@ -3747,19 +3706,19 @@
         <v>28</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>152</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N44" s="6"/>
     </row>
@@ -3787,19 +3746,19 @@
         <v>28</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>151</v>
       </c>
       <c r="M45" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N45" s="6"/>
     </row>
@@ -3808,7 +3767,7 @@
         <v>128</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="6" t="s">
@@ -3827,19 +3786,19 @@
         <v>28</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>111</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M46" s="18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N46" s="6"/>
     </row>
@@ -3867,19 +3826,19 @@
         <v>28</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N47" s="6"/>
     </row>
@@ -3907,19 +3866,19 @@
         <v>28</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>111</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M48" s="18" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N48" s="6"/>
     </row>
@@ -3947,19 +3906,19 @@
         <v>28</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>111</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L49" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M49" s="18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N49" s="6"/>
     </row>
@@ -3987,19 +3946,19 @@
         <v>28</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>111</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M50" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N50" s="6"/>
     </row>
@@ -4027,75 +3986,75 @@
         <v>28</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L51" s="15" t="s">
         <v>151</v>
       </c>
       <c r="M51" s="18" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="J52" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>220</v>
-      </c>
       <c r="K52" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M52" s="18" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="5" t="s">
@@ -4105,38 +4064,38 @@
         <v>28</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M53" s="18" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>27</v>
@@ -4145,38 +4104,38 @@
         <v>28</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M54" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>27</v>
@@ -4185,75 +4144,75 @@
         <v>28</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M55" s="18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="J56" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M56" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="5" t="s">
@@ -4263,75 +4222,75 @@
         <v>28</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M57" s="18" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>233</v>
-      </c>
       <c r="J58" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M58" s="18" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="5" t="s">
@@ -4341,158 +4300,158 @@
         <v>28</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M59" s="18" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F60" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="G60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I60" s="6" t="s">
+      <c r="J60" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="J60" s="6" t="s">
-        <v>290</v>
-      </c>
       <c r="K60" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M60" s="19" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I61" s="6" t="s">
+      <c r="J61" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="J61" s="6" t="s">
-        <v>295</v>
-      </c>
       <c r="K61" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M61" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F62" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>300</v>
-      </c>
       <c r="J62" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M62" s="19" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>28</v>
@@ -4501,118 +4460,118 @@
         <v>28</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L63" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M63" s="19" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F64" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="G64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>310</v>
-      </c>
       <c r="J64" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E65" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="G65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>315</v>
-      </c>
       <c r="J65" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>27</v>
@@ -4621,39 +4580,39 @@
         <v>28</v>
       </c>
       <c r="I66" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="J66" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="K66" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M66" s="19" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E67" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F67" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="G67" s="5" t="s">
         <v>27</v>
       </c>
@@ -4661,39 +4620,39 @@
         <v>28</v>
       </c>
       <c r="I67" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="J67" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="J67" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="K67" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M67" s="19" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F68" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>346</v>
-      </c>
       <c r="G68" s="5" t="s">
         <v>27</v>
       </c>
@@ -4701,119 +4660,119 @@
         <v>28</v>
       </c>
       <c r="I68" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="J68" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="J68" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="K68" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M68" s="19" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="G69" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I69" s="6" t="s">
+      <c r="J69" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="J69" s="6" t="s">
-        <v>329</v>
-      </c>
       <c r="K69" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M69" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>332</v>
-      </c>
       <c r="J70" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E71" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F71" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F71" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="G71" s="5" t="s">
         <v>27</v>
       </c>
@@ -4821,39 +4780,39 @@
         <v>28</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L71" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M71" s="19" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F72" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>340</v>
-      </c>
       <c r="G72" s="5" t="s">
         <v>27</v>
       </c>
@@ -4861,39 +4820,39 @@
         <v>28</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L72" s="15" t="s">
         <v>152</v>
       </c>
       <c r="M72" s="19" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F73" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="F73" s="6" t="s">
-        <v>349</v>
-      </c>
       <c r="G73" s="5" t="s">
         <v>27</v>
       </c>
@@ -4901,39 +4860,39 @@
         <v>28</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>152</v>
       </c>
       <c r="M73" s="19" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F74" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>352</v>
-      </c>
       <c r="G74" s="5" t="s">
         <v>27</v>
       </c>
@@ -4941,38 +4900,38 @@
         <v>28</v>
       </c>
       <c r="I74" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="J74" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="J74" s="6" t="s">
-        <v>355</v>
-      </c>
       <c r="K74" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M74" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>429</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>430</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>27</v>
@@ -4981,35 +4940,35 @@
         <v>28</v>
       </c>
       <c r="I75" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="J75" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="J75" s="6" t="s">
-        <v>441</v>
-      </c>
       <c r="K75" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M75" s="18" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="5" t="s">
@@ -5019,38 +4978,38 @@
         <v>28</v>
       </c>
       <c r="I76" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="J76" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="J76" s="6" t="s">
-        <v>443</v>
-      </c>
       <c r="K76" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M76" s="18" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>27</v>
@@ -5059,35 +5018,35 @@
         <v>28</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M77" s="18" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="5" t="s">
@@ -5097,19 +5056,19 @@
         <v>28</v>
       </c>
       <c r="I78" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J78" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="J78" s="6" t="s">
-        <v>445</v>
-      </c>
       <c r="K78" s="5" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>151</v>
       </c>
       <c r="M78" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N78" s="6"/>
     </row>
